--- a/artfynd/A 29762-2024 artfynd.xlsx
+++ b/artfynd/A 29762-2024 artfynd.xlsx
@@ -786,10 +786,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121150260</v>
+        <v>121150261</v>
       </c>
       <c r="B3" t="n">
-        <v>91975</v>
+        <v>92001</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -798,25 +798,25 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>4366</v>
+        <v>5449</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Skarp dropptaggsvamp</t>
+          <t>Svart taggsvamp</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Hydnellum peckii</t>
+          <t>Phellodon niger</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>Banker</t>
+          <t>(Fr.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -830,10 +830,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>777872</v>
+        <v>777860</v>
       </c>
       <c r="R3" t="n">
-        <v>7380557</v>
+        <v>7380563</v>
       </c>
       <c r="S3" t="n">
         <v>5</v>
@@ -897,10 +897,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121150261</v>
+        <v>121150260</v>
       </c>
       <c r="B4" t="n">
-        <v>91991</v>
+        <v>91985</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -909,25 +909,25 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>5449</v>
+        <v>4366</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Svart taggsvamp</t>
+          <t>Skarp dropptaggsvamp</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Phellodon niger</t>
+          <t>Hydnellum peckii</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P.Karst.</t>
+          <t>Banker</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -941,10 +941,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>777860</v>
+        <v>777872</v>
       </c>
       <c r="R4" t="n">
-        <v>7380563</v>
+        <v>7380557</v>
       </c>
       <c r="S4" t="n">
         <v>5</v>
@@ -1011,7 +1011,7 @@
         <v>121150244</v>
       </c>
       <c r="B5" t="n">
-        <v>91991</v>
+        <v>92001</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>

--- a/artfynd/A 29762-2024 artfynd.xlsx
+++ b/artfynd/A 29762-2024 artfynd.xlsx
@@ -786,7 +786,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121150261</v>
+        <v>121150244</v>
       </c>
       <c r="B3" t="n">
         <v>92001</v>
@@ -830,10 +830,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>777860</v>
+        <v>777670</v>
       </c>
       <c r="R3" t="n">
-        <v>7380563</v>
+        <v>7380396</v>
       </c>
       <c r="S3" t="n">
         <v>5</v>
@@ -860,12 +860,12 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2023-09-27</t>
+          <t>2024-09-04</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2023-09-27</t>
+          <t>2024-09-04</t>
         </is>
       </c>
       <c r="AC3" t="inlineStr">
@@ -1008,7 +1008,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>121150244</v>
+        <v>121150261</v>
       </c>
       <c r="B5" t="n">
         <v>92001</v>
@@ -1052,10 +1052,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>777670</v>
+        <v>777860</v>
       </c>
       <c r="R5" t="n">
-        <v>7380396</v>
+        <v>7380563</v>
       </c>
       <c r="S5" t="n">
         <v>5</v>
@@ -1082,12 +1082,12 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2024-09-04</t>
+          <t>2023-09-27</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2024-09-04</t>
+          <t>2023-09-27</t>
         </is>
       </c>
       <c r="AC5" t="inlineStr">

--- a/artfynd/A 29762-2024 artfynd.xlsx
+++ b/artfynd/A 29762-2024 artfynd.xlsx
@@ -786,10 +786,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121150244</v>
+        <v>121150261</v>
       </c>
       <c r="B3" t="n">
-        <v>92001</v>
+        <v>92013</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -830,10 +830,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>777670</v>
+        <v>777860</v>
       </c>
       <c r="R3" t="n">
-        <v>7380396</v>
+        <v>7380563</v>
       </c>
       <c r="S3" t="n">
         <v>5</v>
@@ -860,12 +860,12 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2024-09-04</t>
+          <t>2023-09-27</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2024-09-04</t>
+          <t>2023-09-27</t>
         </is>
       </c>
       <c r="AC3" t="inlineStr">
@@ -900,7 +900,7 @@
         <v>121150260</v>
       </c>
       <c r="B4" t="n">
-        <v>91985</v>
+        <v>91997</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -1008,10 +1008,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>121150261</v>
+        <v>121150244</v>
       </c>
       <c r="B5" t="n">
-        <v>92001</v>
+        <v>92013</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1052,10 +1052,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>777860</v>
+        <v>777670</v>
       </c>
       <c r="R5" t="n">
-        <v>7380563</v>
+        <v>7380396</v>
       </c>
       <c r="S5" t="n">
         <v>5</v>
@@ -1082,12 +1082,12 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2023-09-27</t>
+          <t>2024-09-04</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2023-09-27</t>
+          <t>2024-09-04</t>
         </is>
       </c>
       <c r="AC5" t="inlineStr">

--- a/artfynd/A 29762-2024 artfynd.xlsx
+++ b/artfynd/A 29762-2024 artfynd.xlsx
@@ -789,7 +789,7 @@
         <v>121150261</v>
       </c>
       <c r="B3" t="n">
-        <v>92013</v>
+        <v>92014</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -900,7 +900,7 @@
         <v>121150260</v>
       </c>
       <c r="B4" t="n">
-        <v>91997</v>
+        <v>91998</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -1011,7 +1011,7 @@
         <v>121150244</v>
       </c>
       <c r="B5" t="n">
-        <v>92013</v>
+        <v>92014</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>

--- a/artfynd/A 29762-2024 artfynd.xlsx
+++ b/artfynd/A 29762-2024 artfynd.xlsx
@@ -786,10 +786,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121150261</v>
+        <v>121150260</v>
       </c>
       <c r="B3" t="n">
-        <v>92014</v>
+        <v>92001</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -798,25 +798,25 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>5449</v>
+        <v>4366</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Svart taggsvamp</t>
+          <t>Skarp dropptaggsvamp</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Phellodon niger</t>
+          <t>Hydnellum peckii</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P.Karst.</t>
+          <t>Banker</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -830,10 +830,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>777860</v>
+        <v>777872</v>
       </c>
       <c r="R3" t="n">
-        <v>7380563</v>
+        <v>7380557</v>
       </c>
       <c r="S3" t="n">
         <v>5</v>
@@ -897,10 +897,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121150260</v>
+        <v>121150261</v>
       </c>
       <c r="B4" t="n">
-        <v>91998</v>
+        <v>92017</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -909,25 +909,25 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>4366</v>
+        <v>5449</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Skarp dropptaggsvamp</t>
+          <t>Svart taggsvamp</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Hydnellum peckii</t>
+          <t>Phellodon niger</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Banker</t>
+          <t>(Fr.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -941,10 +941,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>777872</v>
+        <v>777860</v>
       </c>
       <c r="R4" t="n">
-        <v>7380557</v>
+        <v>7380563</v>
       </c>
       <c r="S4" t="n">
         <v>5</v>
@@ -1011,7 +1011,7 @@
         <v>121150244</v>
       </c>
       <c r="B5" t="n">
-        <v>92014</v>
+        <v>92017</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>

--- a/artfynd/A 29762-2024 artfynd.xlsx
+++ b/artfynd/A 29762-2024 artfynd.xlsx
@@ -786,10 +786,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121150260</v>
+        <v>121150261</v>
       </c>
       <c r="B3" t="n">
-        <v>92001</v>
+        <v>92017</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -798,25 +798,25 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>4366</v>
+        <v>5449</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Skarp dropptaggsvamp</t>
+          <t>Svart taggsvamp</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Hydnellum peckii</t>
+          <t>Phellodon niger</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>Banker</t>
+          <t>(Fr.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -830,10 +830,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>777872</v>
+        <v>777860</v>
       </c>
       <c r="R3" t="n">
-        <v>7380557</v>
+        <v>7380563</v>
       </c>
       <c r="S3" t="n">
         <v>5</v>
@@ -897,7 +897,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121150261</v>
+        <v>121150244</v>
       </c>
       <c r="B4" t="n">
         <v>92017</v>
@@ -941,10 +941,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>777860</v>
+        <v>777670</v>
       </c>
       <c r="R4" t="n">
-        <v>7380563</v>
+        <v>7380396</v>
       </c>
       <c r="S4" t="n">
         <v>5</v>
@@ -971,12 +971,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2023-09-27</t>
+          <t>2024-09-04</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2023-09-27</t>
+          <t>2024-09-04</t>
         </is>
       </c>
       <c r="AC4" t="inlineStr">
@@ -1008,10 +1008,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>121150244</v>
+        <v>121150260</v>
       </c>
       <c r="B5" t="n">
-        <v>92017</v>
+        <v>92001</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1020,25 +1020,25 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>5449</v>
+        <v>4366</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Svart taggsvamp</t>
+          <t>Skarp dropptaggsvamp</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Phellodon niger</t>
+          <t>Hydnellum peckii</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P.Karst.</t>
+          <t>Banker</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
@@ -1052,10 +1052,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>777670</v>
+        <v>777872</v>
       </c>
       <c r="R5" t="n">
-        <v>7380396</v>
+        <v>7380557</v>
       </c>
       <c r="S5" t="n">
         <v>5</v>
@@ -1082,12 +1082,12 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2024-09-04</t>
+          <t>2023-09-27</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2024-09-04</t>
+          <t>2023-09-27</t>
         </is>
       </c>
       <c r="AC5" t="inlineStr">
